--- a/docs/status/king-down-status-2026-10-09.xlsx
+++ b/docs/status/king-down-status-2026-10-09.xlsx
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Each side gets the same six random one-use cards from the deal.</t>
+          <t>Each side starts with the same four random one-use cards from the deal.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The king plus 7 pieces drawn from QORRBBNNAAGMMS, in the same order for both sides.</t>
+          <t>The back rank is drawn from QOLRRBBNNAAGMMS, with one Paladin in the pool.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Paladin out, ogre in (2026-09-24). One beast per army (2026-10-04). Owner 2026-10-09: Paladin back in the pool next to the Ogre (being built).</t>
+          <t>Current pool: src/rules/setup.ts POOL. Paladin and Ogre are built.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="126" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>One beast per army</t>
@@ -4538,12 +4538,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>An army never has two beasts, custom armies included.</t>
+          <t>Each army starts with at most one Beast. Morph cannot create a Beast while that side has one. Salvation or Sacrifice may return a captured Beast even if that gives the side a second Beast.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Owner 2026-10-04.</t>
+          <t>Owner 2026-10-04: no second Beast. Owner 2026-10-09: a second Beast may return through Salvation or Sacrifice.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="78" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Hand size</t>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Six cards a side.</t>
+          <t>Four starting cards per side.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Owner 2026-10-03: six. Owner 2026-10-08: more cards means fewer draws; the question is closed. Draws at d4: none 29.7%, 2 cards 17.5, 3 15.5, 4 12.6, 6 11.0.</t>
+          <t>Owner 2026-10-03: six. Owner 2026-10-08: more cards means fewer draws; the question is closed. Draws at d4: none 29.7%, 2 cards 17.5, 3 15.5, 4 12.6, 6 11.0. Owner 2026-10-09: four starting cards.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The cards the six are dealt from.</t>
+          <t>The cards the starting hand is dealt from.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
